--- a/Controllers.xlsx
+++ b/Controllers.xlsx
@@ -33,9 +33,6 @@
     <t>[ESP32](https://github.com/grblHAL/ESP32)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=BDRING%206-axis%20I2S)</t>
-  </si>
-  <si>
     <t>[Arduino Due](https://store.arduino.cc/arduino-due) with [Arduino Due shield](https://github.com/itadinanta/cnc_mill_prototype/tree/master/arduino_duo_shield)</t>
   </si>
   <si>
@@ -45,75 +42,45 @@
     <t>[Arduino Due](https://store.arduino.cc/arduino-due) with [G2core-DUE-External-Interfaces](https://github.com/cmcgrath5035/G2core-DUE-External-Interfaces)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=SAM3X8E&amp;board=cmgrath%20v3)</t>
-  </si>
-  <si>
     <t>[Arduino Due](https://store.arduino.cc/arduino-due) with [Ramps 1.6](https://reprap.org/wiki/RAMPS_1.6)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=SAM3X8E&amp;board=Ramps%201.6)</t>
-  </si>
-  <si>
     <t>[Bigtreetech Octopus MAX 3](https://github.com/bigtreetech/Octopus-Max-EZ)</t>
   </si>
   <si>
     <t>[STM32H7xx](https://github.com/dresco/STM32H7xx)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32H7xx&amp;board=BTT%20Octopus%20MAX%20H723)</t>
-  </si>
-  <si>
     <t>[Bigtreetech Rodent](https://github.com/bigtreetech/Rodent/tree/master)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=BTT%20Rodent)</t>
-  </si>
-  <si>
     <t>[Bigtreetech Scylla](https://github.com/bigtreetech/Scylla)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32H7xx&amp;board=BTT%20Scylla%20H723)</t>
-  </si>
-  <si>
     <t>[Bigtreetech SKR 2](https://www.bigtree-tech.com/products/bigtreetech-skr-2.html)</t>
   </si>
   <si>
     <t>[STM32F4xx](https://github.com/grblHAL/STM32F4xx)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=BTT%20SKR-2%20STM32F407)</t>
-  </si>
-  <si>
     <t>[Bigtreetech SKR 3](https://biqu.equipment/collections/control-board/products/bigtreetech-btt-skr-3-control-board-for-3d-printer)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32H7xx&amp;board=BTT%20SKR%203)</t>
-  </si>
-  <si>
     <t>[Bigtreetech SKR MINI E3 V2.0](https://www.bigtree-tech.com/products/bigtreetech-skr-mini-e3-v2-0-32-bit-control-board-integrated-tmc2209-uart-for-ender-3.html)</t>
   </si>
   <si>
     <t>[STM32F1xx](https://github.com/grblHAL/STM32F1xx)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F1xx&amp;board=BTT%20SKR%20MINI%20E3%20V2.0%204-axis%20%28Bootloader%29)</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Bigtreetech SKR Pico 1.0](https://biqu.equipment/products/btt-skr-pico-v1-0) </t>
   </si>
   <si>
     <t>[RP2040](https://github.com/grblHAL/RP2040)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=RP2040&amp;board=BTT%20SKR%20Pico%201.0)</t>
-  </si>
-  <si>
     <t>[Bigtreetech SKR PRO](https://www.bigtree-tech.com/products/bigtreetech-skr-pro-v1-2.html)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=BTT%20SKR%20PRO%20v1.2)</t>
-  </si>
-  <si>
     <t>[Bigtreetech SKR v1.3](https://duckduckgo.com/?t=ffsb&amp;q=btt+skr+1.3&amp;ia=web)</t>
   </si>
   <si>
@@ -126,9 +93,6 @@
     <t>[CNC3040](https://github.com/shaise/GrblCNC) with a Red/BluePill</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F1xx&amp;board=CNC%203040%20%28Red/Bluepill%20128K%29)</t>
-  </si>
-  <si>
     <t>[EK-TM4C123GXL LaunchPad](https://www.ti.com/tool/EK-TM4C123GXL) with  [CNC Boosterpack](https://github.com/terjeio/CNC_Boosterpack)</t>
   </si>
   <si>
@@ -144,57 +108,30 @@
     <t xml:space="preserve">[Expatria Technologies PicoBOB G540](https://github.com/Expatria-Technologies/PicoBOB) </t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=RP2040&amp;board=PicoBOB_G540)</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Expatria Technologies PicoBOB](https://github.com/Expatria-Technologies/PicoBOB) </t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=RP2040&amp;board=PicoBOB)</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Flexi-HAL](https://github.com/Expatria-Technologies/Flexi-HAL) </t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Flexi-HAL)</t>
-  </si>
-  <si>
     <t>[Fysetc E4](https://www.fysetc.com/products/fysetc-e4-board-with-built-in-wi-fi-and-bluetooth-4-pcs-tmc2209-240mhz-16m-flash-3d-printer-control-board-based-for-3d-printer?variant=37558333341871)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=Fysetc%20E4%20v1.0)</t>
-  </si>
-  <si>
     <t>[Fysetc S6 V2](https://wiki.fysetc.com/FYSETC_S6/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Fysetc%20S6%20V2.0)</t>
-  </si>
-  <si>
     <t>[Mach 3 USB BOB - BSMCE04U-PP](https://embeddedtronicsblog.wordpress.com/2023/05/17/grbl-running-on-the-4-axis-bsmce04-pp/)&lt;sup&gt;1&lt;/sup&gt;</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F1xx&amp;board=Mach3%20USB%20breakout%20%28BSMCE04U%29)</t>
-  </si>
-  <si>
     <t>[Makerbase MKS-DLC32 MAX](https://github.com/makerbase-mks/MKS-DLC32)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=MKS%20DLC32%20MAX%20v1,%208MB+%20flash)</t>
-  </si>
-  <si>
     <t>[Makerbase MKS-DLC32](https://github.com/makerbase-mks/MKS-DLC32)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=MKS%20DLC32%202.0)</t>
-  </si>
-  <si>
     <t>[Makerbase MKS-TinyBee](https://github.com/makerbase-mks/MKS-TinyBee)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=MKS%20Tinybee%20V1.0)</t>
-  </si>
-  <si>
     <t>[MKS SBASE v1.3](https://github.com/makerbase-mks/MKS-SBASE)</t>
   </si>
   <si>
@@ -219,43 +156,22 @@
     <t>[Nucleo F411RE](https://www.st.com/en/evaluation-tools/nucleo-f411re.html) with [Arduino v3 shield](https://www.makerfabs.com/arduino-cnc-shield-v3.html)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Generic%20Uno/Nucleo-64%20%28STM32F411%29)</t>
-  </si>
-  <si>
     <t>[Nucleo F411RE](https://www.st.com/en/evaluation-tools/nucleo-f411re.html) with [CNC Breakout Nucleo64](https://github.com/terjeio/CNC_Breakout_Nucleo64)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Nucleo-64%20CNC%20Breakout%20%28STM32F411%29)</t>
-  </si>
-  <si>
     <t>[Nucleo F411RE](https://www.st.com/en/evaluation-tools/nucleo-f411re.html) with [Protoneer v3 shield](https://blog.protoneer.co.nz/arduino-cnc-shield/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Protoneer%20v3/Nucleo-64%20%28STM32F411%29)</t>
-  </si>
-  <si>
     <t>[Nucleo F446RE](https://www.st.com/en/evaluation-tools/nucleo-f446re.html) with [Arduino v3 shield](https://www.makerfabs.com/arduino-cnc-shield-v3.html)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Generic%20Uno/Nucleo-64%20%28STM32F446%29)</t>
-  </si>
-  <si>
     <t>[Nucleo F446RE](https://www.st.com/en/evaluation-tools/nucleo-f446re.html) with [CNC Breakout Nucleo64](https://github.com/terjeio/CNC_Breakout_Nucleo64)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Nucleo-64%20CNC%20Breakout%20%28STM32F446%29)</t>
-  </si>
-  <si>
     <t>[Nucleo F446RE](https://www.st.com/en/evaluation-tools/nucleo-f446re.html) with [Protoneer v3 shield](https://blog.protoneer.co.nz/arduino-cnc-shield/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=Protoneer%20v3/Nucleo-64%20%28STM32F446%29)</t>
-  </si>
-  <si>
     <t>[OpenBuilds BlackBox X32](https://openbuildspartstore.com/BlackBox-Motion-Control-System-X32)</t>
-  </si>
-  <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=BlackBox%20X32)</t>
   </si>
   <si>
     <r>
@@ -275,69 +191,39 @@
     </r>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=PiBot%206-axis%20I2S)</t>
-  </si>
-  <si>
     <t>[PiBot V5.88 Ultra](https://www.pibot.com/cnc-laser-electronics/pibot-fluidnc-grblhal-esp32-s3-6-1-axis-cnc-controller-v5-88-ultra)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=PiBot%205.88%20Ultra,%208MB+%20flash)</t>
-  </si>
-  <si>
     <t>[Pi Pico](https://www.raspberrypi.org/products/raspberry-pi-pico/) on [PicoCNC](https://github.com/phil-barrett/PicoCNC)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=RP2040&amp;board=PicoCNC)</t>
-  </si>
-  <si>
     <t>[Protoneer v3](https://blog.protoneer.co.nz/arduino-cnc-shield/) on ESPDuino</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=ESPDUINO-32%20Wemos%20D1%20R32)</t>
-  </si>
-  <si>
     <t>[Radds 1.6](https://reprap.world/electronics/development_boards/radds_v1_6_pre_assembled_3d_printer_board/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=SAM3X8E&amp;board=Radds%201.6)</t>
-  </si>
-  <si>
     <t>[Re-ARM board](https://www.panucatt.com/Re_ARM_for_RAMPS_p/ra1768.htm) with [Ramps 1.6](https://reprap.org/wiki/RAMPS_1.6)</t>
   </si>
   <si>
     <t>[Sienci Labs SuperLongBoard Ext](https://sienci.com/product/slb-ext-closed-loop-controller/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=SuperLongBoard%20External%20%28SLB%20EXT%29)</t>
-  </si>
-  <si>
     <t>[Sienci Labs SuperLongBoard](https://sienci.com/product/slb/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32F4xx&amp;board=SuperLongBoard%20%28SLB%29)</t>
-  </si>
-  <si>
     <t>[SMART Ramps](https://reprap.org/wiki/SMART_RAMPS)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=SAM3X8E&amp;board=Ramps%20SMART)</t>
-  </si>
-  <si>
     <t>[Smoothieboard](https://smoothieware.org/smoothieboard)</t>
   </si>
   <si>
     <t>[Sourcerabbit](https://www.sourcerabbit.com/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=SourceRabbit%204-axis%20CNC)</t>
-  </si>
-  <si>
     <t>[Spark Concepts xPro v5](https://www.spark-concepts.com/cnc-xpro-v5/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=ESP32&amp;board=xPro%20v5)</t>
-  </si>
-  <si>
     <t>[STM32F401CCU6 UNI](https://github.com/Am0k-GIT/STM32F401CCU6_UNI)</t>
   </si>
   <si>
@@ -347,46 +233,160 @@
     <t>[iMXRT1062](https://github.com/grblHAL/iMXRT1062)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=iMXRT1062&amp;board=T40X101)</t>
-  </si>
-  <si>
     <t>[Teensy 4.1](https://www.pjrc.com/store/teensy41.html) on [E5XMCS_T41](https://www.makerstore.com.au/product/elec-e5xmcst41/)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=iMXRT1062&amp;board=E5XMCS_T41)</t>
-  </si>
-  <si>
     <t>[Teensy 4.1](https://www.pjrc.com/store/teensy41.html) on [GRBLHAL2000](https://github.com/Expatria-Technologies/grblhal_2000_PrintNC)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=iMXRT1062&amp;board=GRBLHAL2000%20-%20PRINTNC)</t>
-  </si>
-  <si>
     <t>[Teensy 4.1](https://www.pjrc.com/store/teensy41.html) on [T41BB5X_PRO](https://github.com/phil-barrett/grbl-teensy-4)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=iMXRT1062&amp;board=T41BB5X%20Pro)</t>
-  </si>
-  <si>
     <t>[Teensy 4.1](https://www.pjrc.com/store/teensy41.html) on [T41U5XBB](https://github.com/phil-barrett/grbl-teensy-4)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=iMXRT1062&amp;board=T41U5XBB)</t>
-  </si>
-  <si>
     <t>[WeAct Blackpill](https://github.com/WeActTC/MiniF4-STM32F4x1) on a [Minimal breakout](https://github.com/avizienis/Minimal-Black-Pill--STM32F4xx-BOB-for-grblHAL)</t>
   </si>
   <si>
     <t>[WeAct MiniSTM32H7xx](https://github.com/WeActTC/MiniSTM32H7xx)</t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=STM32H7xx&amp;board=WeAct%20Mini%20H743)</t>
-  </si>
-  <si>
     <t xml:space="preserve">[Bolangsk](https://www.bolangsk.cn/rp2350-grblhal-control-board/) </t>
   </si>
   <si>
-    <t>[WebBuilder](https://svn.io-engineering.com:8443/?driver=RP2040&amp;board=Bolangsk)</t>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=BDRING%206-axis%20I2S)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=SAM3X8E&amp;board=cmgrath%20v3)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=SAM3X8E&amp;board=Ramps%201.6)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32H7xx&amp;board=BTT%20Octopus%20MAX%20H723)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=BTT%20Rodent)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32H7xx&amp;board=BTT%20Scylla%20H723)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=BTT%20SKR-2%20STM32F407)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32H7xx&amp;board=BTT%20SKR%203)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F1xx&amp;board=BTT%20SKR%20MINI%20E3%20V2.0%204-axis%20%28Bootloader%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=RP2040&amp;board=BTT%20SKR%20Pico%201.0)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=BTT%20SKR%20PRO%20v1.2)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=RP2040&amp;board=Bolangsk)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F1xx&amp;board=CNC%203040%20%28Red/Bluepill%20128K%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=RP2040&amp;board=PicoBOB_G540)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=RP2040&amp;board=PicoBOB)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Flexi-HAL)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=Fysetc%20E4%20v1.0)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Fysetc%20S6%20V2.0)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F1xx&amp;board=Mach3%20USB%20breakout%20%28BSMCE04U%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=MKS%20DLC32%20MAX%20v1,%208MB+%20flash)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=MKS%20DLC32%202.0)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=MKS%20Tinybee%20V1.0)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Generic%20Uno/Nucleo-64%20%28STM32F411%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Nucleo-64%20CNC%20Breakout%20%28STM32F411%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Protoneer%20v3/Nucleo-64%20%28STM32F411%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Generic%20Uno/Nucleo-64%20%28STM32F446%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Nucleo-64%20CNC%20Breakout%20%28STM32F446%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=Protoneer%20v3/Nucleo-64%20%28STM32F446%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=BlackBox%20X32)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=PiBot%206-axis%20I2S)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=PiBot%205.88%20Ultra,%208MB+%20flash)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=RP2040&amp;board=PicoCNC)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=ESPDUINO-32%20Wemos%20D1%20R32)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=SAM3X8E&amp;board=Radds%201.6)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=SuperLongBoard%20External%20%28SLB%20EXT%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32F4xx&amp;board=SuperLongBoard%20%28SLB%29)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=SAM3X8E&amp;board=Ramps%20SMART)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=SourceRabbit%204-axis%20CNC)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=ESP32&amp;board=xPro%20v5)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=iMXRT1062&amp;board=T40X101)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=iMXRT1062&amp;board=E5XMCS_T41)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=iMXRT1062&amp;board=GRBLHAL2000%20-%20PRINTNC)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=iMXRT1062&amp;board=T41BB5X%20Pro)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=iMXRT1062&amp;board=T41U5XBB)</t>
+  </si>
+  <si>
+    <t>[WebBuilder](https://webbuilder.grblhal.org/?driver=STM32H7xx&amp;board=WeAct%20Mini%20H743)</t>
   </si>
 </sst>
 </file>
@@ -693,595 +693,595 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>41</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
       </c>
       <c r="C50" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
       </c>
       <c r="C51" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C53" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C55" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
